--- a/docagent_clean_mvp/sample_data/raw_excels/CAIQ_SetB.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/CAIQ_SetB.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>All data at rest is encrypted using AES-256, with key rotation performed every 90 days.</t>
+          <t>Standard Encryption &amp; Key Management control mandates that all data at rest is encrypted using AES-256, with key rotation performed every 90 days. [CAIQ-061]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Compliant - key rotation logs attached</t>
+          <t>Compliant - last reviewed this cycle</t>
         </is>
       </c>
     </row>
